--- a/Безработица_РФ_2015_2025.xlsx
+++ b/Безработица_РФ_2015_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\CS292\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0E2BFE1-42C1-4DDD-B75E-0E453723EB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{FFCE53AA-2F41-491B-AB9D-E816E401E3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8820" yWindow="4095" windowWidth="28560" windowHeight="16125" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Безработица РФ" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Год</t>
   </si>
@@ -62,16 +62,25 @@
   <si>
     <t>Δ</t>
   </si>
+  <si>
+    <t>Размер датасета</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уровень безработицы (%) в России c 15 до 72 лет </t>
+  </si>
+  <si>
+    <t>https://rosstat.gov.ru/storage/mediabank/trud_1_15-72.xlsx</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="172" formatCode="0.00000000"/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.00000000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +92,23 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -117,10 +143,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -137,17 +164,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -179,7 +212,17 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.6946669268957277E-2"/>
+          <c:y val="2.5584494245911568E-2"/>
+          <c:w val="0.91305326279329679"/>
+          <c:h val="0.82647694871634991"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -215,7 +258,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Безработица РФ'!$A$2:$A$12</c:f>
+              <c:f>'Безработица РФ'!$A$4:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -257,7 +300,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Безработица РФ'!$C$2:$C$12</c:f>
+              <c:f>'Безработица РФ'!$C$4:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="11"/>
@@ -336,7 +379,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Безработица РФ'!$F$2:$F$12</c:f>
+              <c:f>'Безработица РФ'!$F$4:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>0.00000000</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1217,16 +1260,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>942974</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>14286</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>85724</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>514351</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1539,12 +1582,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
@@ -1552,371 +1595,387 @@
     <col min="9" max="9" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>8</v>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>2015</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6">
-        <v>5.6</v>
-      </c>
-      <c r="D2" s="2">
-        <f>B2*B2</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <f>B2*C2</f>
-        <v>5.6</v>
-      </c>
-      <c r="F2" s="7">
-        <f>$A$16*B2 + $B$16</f>
-        <v>5.9590909090909099</v>
-      </c>
-      <c r="G2" s="7">
-        <f>(C2-F2)^2</f>
-        <v>0.12894628099173636</v>
+      <c r="A2" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2016</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6">
-        <v>5.5</v>
-      </c>
-      <c r="D3" s="2">
-        <f t="shared" ref="D3:D12" si="0">B3*B3</f>
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="7">
-        <f t="shared" ref="E3:E12" si="1">B3*C3</f>
-        <v>11</v>
-      </c>
-      <c r="F3" s="7">
-        <f t="shared" ref="F3:F12" si="2">$A$16*B3 + $B$16</f>
-        <v>5.6545454545454552</v>
-      </c>
-      <c r="G3" s="7">
-        <f t="shared" ref="G3:G12" si="3">(C3-F3)^2</f>
-        <v>2.388429752066136E-2</v>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B4" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="6">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E4" s="7">
-        <f t="shared" si="1"/>
-        <v>15.600000000000001</v>
+        <f>B4*B4</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="9">
+        <f>B4*C4</f>
+        <v>5.6</v>
       </c>
       <c r="F4" s="7">
-        <f t="shared" si="2"/>
-        <v>5.3500000000000005</v>
+        <f t="shared" ref="F4:F14" si="0">$A$18*B4 + $B$18</f>
+        <v>5.9590909090909099</v>
       </c>
       <c r="G4" s="7">
-        <f t="shared" si="3"/>
-        <v>2.2500000000000107E-2</v>
+        <f>(C4-F4)^2</f>
+        <v>0.12894628099173636</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" ref="D5:D14" si="1">B5*B5</f>
         <v>4</v>
       </c>
-      <c r="C5" s="6">
-        <v>4.8</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="E5" s="9">
+        <f t="shared" ref="E5:E14" si="2">B5*C5</f>
+        <v>11</v>
+      </c>
+      <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" si="1"/>
-        <v>19.2</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="2"/>
-        <v>5.0454545454545467</v>
+        <v>5.6545454545454552</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" si="3"/>
-        <v>6.0247933884298242E-2</v>
+        <f t="shared" ref="G5:G14" si="3">(C5-F5)^2</f>
+        <v>2.388429752066136E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B6" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" s="6">
-        <v>4.5999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" si="2"/>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="E6" s="7">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="2"/>
-        <v>4.7409090909090921</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="G6" s="7">
         <f t="shared" si="3"/>
-        <v>1.9855371900826875E-2</v>
+        <v>2.2500000000000107E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B7" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="6">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="2"/>
+        <v>19.2</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="E7" s="7">
-        <f t="shared" si="1"/>
-        <v>34.799999999999997</v>
-      </c>
-      <c r="F7" s="7">
-        <f t="shared" si="2"/>
-        <v>4.4363636363636374</v>
+        <v>5.0454545454545467</v>
       </c>
       <c r="G7" s="7">
         <f t="shared" si="3"/>
-        <v>1.8595041322314017</v>
+        <v>6.0247933884298242E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B8" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" s="6">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" si="1"/>
-        <v>33.6</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" si="2"/>
-        <v>4.1318181818181827</v>
+        <v>4.7409090909090921</v>
       </c>
       <c r="G8" s="7">
         <f t="shared" si="3"/>
-        <v>0.44646694214875887</v>
+        <v>1.9855371900826875E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B9" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="D9" s="2">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="2"/>
+        <v>34.799999999999997</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="E9" s="7">
-        <f t="shared" si="1"/>
-        <v>31.2</v>
-      </c>
-      <c r="F9" s="7">
-        <f t="shared" si="2"/>
-        <v>3.827272727272728</v>
+        <v>4.4363636363636374</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="3"/>
-        <v>5.2892561983469821E-3</v>
+        <v>1.8595041322314017</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B10" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="6">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="D10" s="2">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="2"/>
+        <v>33.6</v>
+      </c>
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="E10" s="7">
-        <f t="shared" si="1"/>
-        <v>28.8</v>
-      </c>
-      <c r="F10" s="7">
-        <f t="shared" si="2"/>
-        <v>3.5227272727272734</v>
+        <v>4.1318181818181827</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" si="3"/>
-        <v>0.10415289256198378</v>
+        <v>0.44646694214875887</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B11" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="D11" s="2">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="2"/>
+        <v>31.2</v>
+      </c>
+      <c r="F11" s="7">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" si="2"/>
-        <v>3.2181818181818187</v>
+        <v>3.827272727272728</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="3"/>
-        <v>0.10123966942148799</v>
+        <v>5.2892561983469821E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="D12" s="2">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="2"/>
+        <v>28.8</v>
+      </c>
+      <c r="F12" s="7">
         <f t="shared" si="0"/>
-        <v>121</v>
-      </c>
-      <c r="E12" s="7">
-        <f t="shared" si="1"/>
-        <v>27.5</v>
-      </c>
-      <c r="F12" s="7">
-        <f t="shared" si="2"/>
-        <v>2.9136363636363645</v>
+        <v>3.5227272727272734</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" si="3"/>
-        <v>0.17109504132231473</v>
+        <v>0.10415289256198378</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5">
-        <f>SUM(B2:B12)</f>
-        <v>66</v>
-      </c>
-      <c r="C13" s="5">
-        <f>SUM(C2:C12)</f>
-        <v>48.800000000000004</v>
-      </c>
-      <c r="D13" s="5">
-        <f>SUM(D2:D12)</f>
-        <v>506</v>
-      </c>
-      <c r="E13" s="5">
-        <f>SUM(E2:E12)</f>
-        <v>259.3</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="8">
-        <f>SUM(G2:G12)</f>
-        <v>2.943181818181817</v>
+      <c r="A13" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="0"/>
+        <v>3.2181818181818187</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="3"/>
+        <v>0.10123966942148799</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="E14" s="9">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="0"/>
+        <v>2.9136363636363645</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="3"/>
+        <v>0.17109504132231473</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5">
+        <f>SUM(B4:B14)</f>
+        <v>66</v>
+      </c>
+      <c r="C15" s="5">
+        <f>SUM(C4:C14)</f>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="D15" s="5">
+        <f>SUM(D4:D14)</f>
+        <v>506</v>
+      </c>
+      <c r="E15" s="5">
+        <f>SUM(E4:E14)</f>
+        <v>259.3</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="8">
+        <f>SUM(G4:G14)</f>
+        <v>2.943181818181817</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <f>(B12*E13 - B13*C13)/(B12*D13 - B13^2)</f>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <f>(A21*E15 - B15*C15)/(B14*D15 - B15^2)</f>
         <v>-0.30454545454545456</v>
       </c>
-      <c r="B16" s="5">
-        <f>(C13 - A16*B13)/B12</f>
+      <c r="B18" s="5">
+        <f>(C15 - A18*B15)/B14</f>
         <v>6.2636363636363646</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
